--- a/PROJECT MAOLIN New/chinese/Craveva_Full Inventory List_全庫存明細表.xlsx
+++ b/PROJECT MAOLIN New/chinese/Craveva_Full Inventory List_全庫存明細表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\web\craveva-staging\PROJECT MAOLIN New\chinese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276734EB-ECB2-4A6B-9531-CA791771A536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFE0FDF-8918-4147-B2D4-48A34E99E3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9400,13 +9400,13 @@
     <t xml:space="preserve">20250807            </t>
   </si>
   <si>
-    <t>批號庫存狀況</t>
-  </si>
-  <si>
     <t>※顯示未結案；庫存量＞0的批號；有效天數]&gt;1；扣處待報廢/待處理</t>
   </si>
   <si>
     <t>最後更新日: 2026/03/19</t>
+  </si>
+  <si>
+    <t>批號庫存狀況 | Batch number inventory status</t>
   </si>
 </sst>
 </file>
@@ -9885,7 +9885,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:J2847"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0.5703125" customWidth="1"/>
     <col min="2" max="2" width="0.42578125" customWidth="1"/>
@@ -9903,7 +9903,7 @@
     <row r="1" spans="2:10" s="1" customFormat="1" ht="5.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:10" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="13" t="s">
-        <v>3126</v>
+        <v>3128</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -9917,7 +9917,7 @@
     <row r="3" spans="2:10" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="4" spans="2:10" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="14" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -9927,7 +9927,7 @@
     <row r="5" spans="2:10" s="1" customFormat="1" ht="2.65" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="6" spans="2:10" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="12" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="7" spans="2:10" s="1" customFormat="1" ht="6.95" customHeight="1" x14ac:dyDescent="0.15"/>
